--- a/artfynd/A 27884-2025 artfynd.xlsx
+++ b/artfynd/A 27884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017445</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017444</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017025</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27884-2025 artfynd.xlsx
+++ b/artfynd/A 27884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017445</v>
       </c>
       <c r="B2" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017444</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017025</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27884-2025 artfynd.xlsx
+++ b/artfynd/A 27884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017445</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017444</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017025</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27884-2025 artfynd.xlsx
+++ b/artfynd/A 27884-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017445</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017444</v>
       </c>
       <c r="B3" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017025</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27884-2025 artfynd.xlsx
+++ b/artfynd/A 27884-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126017445</v>
+        <v>78528768</v>
       </c>
       <c r="B2" t="n">
-        <v>80083</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tevansjö, Hls</t>
+          <t>Skarpen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526428</v>
+        <v>526515</v>
       </c>
       <c r="R2" t="n">
-        <v>6883093</v>
+        <v>6882962</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2019-06-13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Caspar Ström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126017444</v>
+        <v>126017025</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526316</v>
+        <v>526350</v>
       </c>
       <c r="R3" t="n">
-        <v>6883120</v>
+        <v>6883096</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -850,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -887,10 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126017025</v>
+        <v>126017055</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>526350</v>
+        <v>526337</v>
       </c>
       <c r="R4" t="n">
-        <v>6883096</v>
+        <v>6883137</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -956,12 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -990,6 +981,315 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126017444</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tevansjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>526316</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6883120</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126017445</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tevansjö, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>526428</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6883093</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>78528769</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skarpen, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>526526</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6882960</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-06-13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Caspar Ström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27884-2025 artfynd.xlsx
+++ b/artfynd/A 27884-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78528768</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017055</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017444</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017445</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,8 +1320,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78528769</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>